--- a/all_stations.xlsx
+++ b/all_stations.xlsx
@@ -5746,9 +5746,14 @@
           <t>CIELĘTNIKI</t>
         </is>
       </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>[19.57361111111111, 50.8875]</t>
+        </is>
+      </c>
       <c r="E265" s="1" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
@@ -20606,9 +20611,14 @@
           <t>LUTOL SUCHY</t>
         </is>
       </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>[15.716944444444444, 52.337500000000006]</t>
+        </is>
+      </c>
       <c r="E1006" s="1" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
@@ -25363,9 +25373,14 @@
           <t>NOWA WIEŚ WIELKA II</t>
         </is>
       </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>[18.083333333333332, 52.97916666666667]</t>
+        </is>
+      </c>
       <c r="E1243" s="1" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
@@ -26273,9 +26288,14 @@
           <t>OCHABY</t>
         </is>
       </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>[18.76527777777778, 49.844166666666666]</t>
+        </is>
+      </c>
       <c r="E1289" s="1" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
@@ -31147,9 +31167,14 @@
           <t>RABA NIŻNA</t>
         </is>
       </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>[20.048611111111114, 49.657222222222224]</t>
+        </is>
+      </c>
       <c r="E1531" s="1" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
@@ -33475,9 +33500,14 @@
           <t>SADKOWICE</t>
         </is>
       </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>[20.5175, 51.72555555555556]</t>
+        </is>
+      </c>
       <c r="E1643" s="1" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
@@ -34257,9 +34287,14 @@
           <t>SIEMIANOWICE ŚLĄSKIE</t>
         </is>
       </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>[19.022777777777776, 50.3275]</t>
+        </is>
+      </c>
       <c r="E1683" s="1" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
@@ -35495,9 +35530,14 @@
           <t>SŁUPIA WIELKA</t>
         </is>
       </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>[17.227777777777778, 52.221111111111114]</t>
+        </is>
+      </c>
       <c r="E1745" s="1" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
@@ -39597,9 +39637,14 @@
           <t>ŚREM</t>
         </is>
       </c>
+      <c r="C1951" t="inlineStr">
+        <is>
+          <t>[17.029999999999998, 52.0925]</t>
+        </is>
+      </c>
       <c r="E1951" s="1" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>

--- a/all_stations.xlsx
+++ b/all_stations.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2400"/>
+  <dimension ref="A1:E2403"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.625" defaultRowHeight="14.3"/>
   <cols>
     <col width="13.625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -48779,6 +48779,72 @@
         </is>
       </c>
       <c r="E2400" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2401">
+      <c r="A2401" t="inlineStr">
+        <is>
+          <t>249220390</t>
+        </is>
+      </c>
+      <c r="B2401" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="C2401" t="inlineStr">
+        <is>
+          <t>[22.18722222222222, 49.87111111111111]</t>
+        </is>
+      </c>
+      <c r="E2401" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2402">
+      <c r="A2402" t="inlineStr">
+        <is>
+          <t>252150370</t>
+        </is>
+      </c>
+      <c r="B2402" t="inlineStr">
+        <is>
+          <t>PRZYPROSTYNIA</t>
+        </is>
+      </c>
+      <c r="C2402" t="inlineStr">
+        <is>
+          <t>[15.931666666666667, 52.23027777777778]</t>
+        </is>
+      </c>
+      <c r="E2402" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2403">
+      <c r="A2403" t="inlineStr">
+        <is>
+          <t>252190260</t>
+        </is>
+      </c>
+      <c r="B2403" t="inlineStr">
+        <is>
+          <t>CHĄŚNO</t>
+        </is>
+      </c>
+      <c r="C2403" t="inlineStr">
+        <is>
+          <t>[19.919444444444444, 52.16166666666666]</t>
+        </is>
+      </c>
+      <c r="E2403" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
